--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.QA.FRM.04.01. Yıkama Öncesi Mal Kabul Kontrol Formu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.QA.FRM.04.01. Yıkama Öncesi Mal Kabul Kontrol Formu.xlsx
@@ -412,7 +412,7 @@
 مشرف قسم الغسيل</t>
   </si>
   <si>
-    <t>EG.QA.FRM.04.01</t>
+    <t>EMS.QA.FRM.04.01</t>
   </si>
 </sst>
 </file>
